--- a/data/trans_dic/IP28_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP28_R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura</t>
+          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,93</t>
+          <t>0,0; 7,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,75</t>
+          <t>0,0; 7,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,64</t>
+          <t>0,0; 6,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 10,95</t>
+          <t>1,18; 12,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,3</t>
+          <t>0,95; 8,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,45</t>
+          <t>0,0; 7,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,81</t>
+          <t>0,61; 6,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,97</t>
+          <t>0,65; 5,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,19</t>
+          <t>1,06; 6,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,16</t>
+          <t>0,62; 5,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,8</t>
+          <t>0,66; 4,16</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,39</t>
+          <t>0,65; 6,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,95</t>
+          <t>0,0; 5,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,92</t>
+          <t>0,0; 3,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,92</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,19</t>
+          <t>0,0; 3,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,83</t>
+          <t>0,0; 4,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,69</t>
+          <t>0,0; 5,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,0; 4,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,46</t>
+          <t>0,32; 3,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,68</t>
+          <t>0,36; 3,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,6</t>
+          <t>0,29; 2,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,57 +997,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,75</t>
+          <t>0,0; 8,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,66</t>
+          <t>0,0; 5,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,3</t>
+          <t>0,0; 6,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,17</t>
+          <t>0,0; 4,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,38</t>
+          <t>0,0; 2,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,14</t>
+          <t>0,53; 4,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,18</t>
+          <t>0,0; 5,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,25</t>
+          <t>0,0; 6,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,34</t>
+          <t>0,0; 7,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 12,24</t>
+          <t>1,43; 11,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 3,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,38</t>
+          <t>0,0; 8,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,54</t>
+          <t>0,0; 4,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,22</t>
+          <t>0,39; 3,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,52</t>
+          <t>0,44; 4,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,26</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,83</t>
+          <t>0,61; 6,45</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,78</t>
+          <t>0,0; 7,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,19</t>
+          <t>0,0; 9,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,17</t>
+          <t>0,0; 7,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,44</t>
+          <t>0,0; 7,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,79</t>
+          <t>0,0; 9,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,73</t>
+          <t>0,0; 11,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,92</t>
+          <t>0,0; 4,82</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,28</t>
+          <t>0,8; 7,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,13</t>
+          <t>0,0; 4,99</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,19</t>
+          <t>0,0; 5,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,29; 11,56</t>
+          <t>1,3; 10,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,87</t>
+          <t>0,0; 5,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,03</t>
+          <t>0,0; 8,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,1</t>
+          <t>0,0; 7,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,06</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,3</t>
+          <t>1,3; 7,27</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,71</t>
+          <t>0,0; 3,09</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,03</t>
+          <t>0,0; 3,59</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,31</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,2</t>
+          <t>0,0; 2,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,85</t>
+          <t>0,5; 4,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 6,7</t>
+          <t>0,54; 6,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,52</t>
+          <t>0,0; 3,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,0</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,35</t>
+          <t>0,51; 4,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,84</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,52</t>
+          <t>0,28; 2,66</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,07</t>
+          <t>0,25; 2,04</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,68</t>
+          <t>0,81; 3,91</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,19</t>
+          <t>0,7; 3,72</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,53</t>
+          <t>0,73; 4,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,18</t>
+          <t>0,91; 5,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,92</t>
+          <t>0,0; 2,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,64</t>
+          <t>0,45; 4,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,97</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,1</t>
+          <t>0,65; 3,02</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,58</t>
+          <t>0,91; 3,48</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,63</t>
+          <t>0,18; 1,66</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,17</t>
+          <t>0,72; 2,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,03</t>
+          <t>1,16; 3,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,81</t>
+          <t>0,5; 1,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,56</t>
+          <t>0,78; 2,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,99</t>
+          <t>0,66; 2,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,63</t>
+          <t>0,99; 2,59</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,73</t>
+          <t>0,49; 1,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,78</t>
+          <t>0,49; 1,82</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,81</t>
+          <t>0,83; 1,82</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,59</t>
+          <t>1,33; 2,52</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,55</t>
+          <t>0,62; 1,51</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,78</t>
+          <t>0,77; 1,78</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1312</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2835</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1832</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1261</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1793</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2835</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3145</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3088</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4147</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3770</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4803</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>710; 7322</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>570; 5125</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3951</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>482; 5125</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>721; 6429</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1198; 7343</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>624; 5160</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1010; 6357</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2309</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2957</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2894</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1923</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1728</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>658; 6622</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5227</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3174</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3637</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3266</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4029</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5168</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5586</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>665; 6802</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>706; 6663</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>564; 5401</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5414</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1495</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1265</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1265</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2146</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5139</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3412</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4395</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2797</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3817</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>651; 5637</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3319</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1252</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1448</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3730</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1845</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1397</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3730</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4433</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4492</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5153</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1003; 8370</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3032</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6094</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3400</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>584; 4842</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>645; 6812</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4414</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>900; 9570</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2046</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3203</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3690</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3282</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3343</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4216</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4835</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4179</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>644; 5742</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3544</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3753</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2204</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1452</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>3656</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3265</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>705; 5900</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2781</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4945</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4024</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3223</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>1435; 8027</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3087</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3676</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>733</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2591</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>3149</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1270</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2107</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1684</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>2178</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>1935</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>4698</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>4833</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3235</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3181</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>631; 5996</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>676; 7912</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 5059</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4438</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>669; 5646</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 5855</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>718; 6931</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>622; 5146</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2070; 9982</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>1962; 10410</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>3256</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>3601</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2599</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1297</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>4615</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>1821</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>1132; 7105</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>1372; 7998</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2652</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4775</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>739; 6681</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3967</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 5258</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>2043; 9560</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>2861; 10971</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>513; 4837</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4316</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>8832</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>13052</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>6372</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>9542</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>8810</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>11419</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>6661</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>7453</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>17642</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>24471</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>13033</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>16995</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>4849; 15464</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>7527; 20054</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>3196; 11478</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>5190; 17119</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>4692; 14804</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>6807; 17821</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>3251; 11437</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>3703; 13771</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>11499; 25294</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>17707; 33627</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>8073; 19699</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>10908; 25233</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP28_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP28_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
+          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -722,57 +722,57 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,91</t>
+          <t>0,0; 8,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,94</t>
+          <t>0,0; 6,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,55</t>
+          <t>0,0; 6,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 12,16</t>
+          <t>1,18; 10,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,52</t>
+          <t>0,94; 8,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,51</t>
+          <t>0,0; 8,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,46</t>
+          <t>0,61; 6,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,83</t>
+          <t>0,64; 6,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 6,52</t>
+          <t>1,07; 6,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,16</t>
+          <t>0,62; 5,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,16</t>
+          <t>0,71; 4,5</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,56</t>
+          <t>0,65; 6,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,4</t>
+          <t>0,0; 5,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,38</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 4,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,05</t>
+          <t>0,0; 4,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,06</t>
+          <t>0,0; 4,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,38</t>
+          <t>0,0; 3,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,25</t>
+          <t>0,32; 3,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,4</t>
+          <t>0,35; 3,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,75</t>
+          <t>0,29; 3,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,57</t>
+          <t>0,0; 7,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,17 +1012,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,86</t>
+          <t>0,0; 5,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,25</t>
+          <t>0,0; 6,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,45</t>
+          <t>0,0; 5,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,78</t>
+          <t>0,0; 3,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,59</t>
+          <t>0,53; 4,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,65</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
     </row>
@@ -1137,37 +1137,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,97</t>
+          <t>0,0; 5,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 7,61</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,88</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1,37; 12,31</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 3,85</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 6,25</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,17</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1,43; 11,93</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,93</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,25</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,83</t>
+          <t>0,0; 4,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,22 +1177,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,2</t>
+          <t>0,39; 3,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,68</t>
+          <t>0,45; 4,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,45</t>
+          <t>0,64; 6,24</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,65</t>
+          <t>0,0; 7,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,8</t>
+          <t>0,0; 10,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,79</t>
+          <t>0,0; 6,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,45</t>
+          <t>0,0; 7,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,79</t>
+          <t>0,0; 9,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,87</t>
+          <t>0,0; 10,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,82</t>
+          <t>0,0; 5,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,12</t>
+          <t>0,79; 6,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>0,0; 4,43</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,99</t>
+          <t>0,0; 5,6</t>
         </is>
       </c>
     </row>
@@ -1417,17 +1417,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,9</t>
+          <t>0,0; 4,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,3; 10,88</t>
+          <t>1,31; 12,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,43</t>
+          <t>0,0; 6,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,8</t>
+          <t>0,0; 9,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1452,27 +1452,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,16</t>
+          <t>0,0; 7,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,27</t>
+          <t>1,29; 6,83</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 3,71</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 3,9</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,78</t>
+          <t>0,5; 4,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 6,35</t>
+          <t>0,71; 7,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,78</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,98</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,35</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>0,0; 3,79</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,42</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0,51; 4,34</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,77</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,66</t>
+          <t>0,28; 2,23</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,04</t>
+          <t>0,25; 2,07</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,91</t>
+          <t>0,81; 3,84</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,72</t>
+          <t>0,58; 3,72</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,59</t>
+          <t>0,79; 4,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,3</t>
+          <t>0,88; 4,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1717,42 +1717,42 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,94</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,07</t>
+          <t>0,39; 3,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,42</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,02</t>
+          <t>0,66; 3,1</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,48</t>
+          <t>0,94; 3,42</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,66</t>
+          <t>0,18; 1,92</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,31</t>
+          <t>0,73; 2,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,1</t>
+          <t>1,28; 3,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,81</t>
+          <t>0,51; 1,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,58</t>
+          <t>0,76; 2,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,07</t>
+          <t>0,68; 2,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,59</t>
+          <t>1,01; 2,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,71</t>
+          <t>0,49; 1,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,82</t>
+          <t>0,49; 1,78</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,82</t>
+          <t>0,86; 1,83</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,52</t>
+          <t>1,28; 2,52</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,51</t>
+          <t>0,63; 1,55</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,78</t>
+          <t>0,74; 1,83</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
+          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2214,57 +2214,57 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4147</t>
+          <t>0; 4684</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3770</t>
+          <t>0; 3096</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4803</t>
+          <t>0; 4484</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>710; 7322</t>
+          <t>708; 6458</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>570; 5125</t>
+          <t>567; 5044</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3951</t>
+          <t>0; 4432</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>482; 5125</t>
+          <t>488; 5280</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>721; 6429</t>
+          <t>708; 7025</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1198; 7343</t>
+          <t>1210; 7121</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>624; 5160</t>
+          <t>621; 5701</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1010; 6357</t>
+          <t>1087; 6870</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>658; 6622</t>
+          <t>657; 6375</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5227</t>
+          <t>0; 5775</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3174</t>
+          <t>0; 2337</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3637</t>
+          <t>0; 5023</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3266</t>
+          <t>0; 2619</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4029</t>
+          <t>0; 4109</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5168</t>
+          <t>0; 4676</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5586</t>
+          <t>0; 4953</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>665; 6802</t>
+          <t>661; 6897</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>706; 6663</t>
+          <t>678; 7332</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>564; 5401</t>
+          <t>570; 5934</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 5414</t>
+          <t>0; 6221</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5139</t>
+          <t>0; 4691</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2640,17 +2640,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3412</t>
+          <t>0; 3338</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4395</t>
+          <t>0; 4421</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2797</t>
+          <t>0; 3550</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2665,12 +2665,12 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3817</t>
+          <t>0; 4453</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>651; 5637</t>
+          <t>648; 5756</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3319</t>
+          <t>0; 3637</t>
         </is>
       </c>
     </row>
@@ -2833,37 +2833,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4433</t>
+          <t>0; 4444</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4492</t>
+          <t>0; 5464</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5153</t>
+          <t>0; 4226</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1003; 8370</t>
+          <t>960; 8637</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3032</t>
+          <t>0; 2975</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6094</t>
+          <t>0; 4615</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3400</t>
+          <t>0; 3230</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2873,22 +2873,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>584; 4842</t>
+          <t>594; 4880</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>645; 6812</t>
+          <t>654; 6556</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 4414</t>
+          <t>0; 4338</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>900; 9570</t>
+          <t>950; 9252</t>
         </is>
       </c>
     </row>
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3203</t>
+          <t>0; 3275</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3690</t>
+          <t>0; 3808</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3282</t>
+          <t>0; 2856</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3343</t>
+          <t>0; 3509</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4216</t>
+          <t>0; 3989</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3076,27 +3076,27 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4835</t>
+          <t>0; 4266</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4179</t>
+          <t>0; 4596</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>644; 5742</t>
+          <t>640; 4981</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 3544</t>
+          <t>0; 3842</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3753</t>
+          <t>0; 4213</t>
         </is>
       </c>
     </row>
@@ -3249,17 +3249,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3265</t>
+          <t>0; 2606</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>705; 5900</t>
+          <t>712; 6516</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2781</t>
+          <t>0; 3406</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4945</t>
+          <t>0; 5141</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3284,27 +3284,27 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4024</t>
+          <t>0; 3964</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3223</t>
+          <t>0; 3488</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1435; 8027</t>
+          <t>1426; 7539</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 3087</t>
+          <t>0; 3709</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 3676</t>
+          <t>0; 3996</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3235</t>
+          <t>0; 3656</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 3181</t>
+          <t>0; 3434</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>631; 5996</t>
+          <t>625; 5599</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>676; 7912</t>
+          <t>878; 8718</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 5059</t>
+          <t>0; 5058</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 4438</t>
+          <t>0; 3864</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>669; 5646</t>
+          <t>0; 5650</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 5855</t>
+          <t>0; 5883</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>718; 6931</t>
+          <t>718; 5808</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>622; 5146</t>
+          <t>620; 5213</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2070; 9982</t>
+          <t>2079; 9804</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1962; 10410</t>
+          <t>1630; 10406</t>
         </is>
       </c>
     </row>
@@ -3665,17 +3665,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1132; 7105</t>
+          <t>1229; 7354</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1372; 7998</t>
+          <t>1321; 7323</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 2652</t>
+          <t>0; 2656</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3685,42 +3685,42 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 4775</t>
+          <t>0; 4778</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>739; 6681</t>
+          <t>635; 6317</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 3967</t>
+          <t>0; 3953</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 5258</t>
+          <t>0; 4483</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2043; 9560</t>
+          <t>2104; 9807</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2861; 10971</t>
+          <t>2949; 10786</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>513; 4837</t>
+          <t>525; 5588</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 4316</t>
+          <t>0; 4571</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>4849; 15464</t>
+          <t>4925; 14519</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>7527; 20054</t>
+          <t>8273; 19521</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3196; 11478</t>
+          <t>3221; 11189</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5190; 17119</t>
+          <t>5014; 16868</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4692; 14804</t>
+          <t>4886; 14795</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6807; 17821</t>
+          <t>6996; 18066</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3251; 11437</t>
+          <t>3262; 11672</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>3703; 13771</t>
+          <t>3723; 13517</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>11499; 25294</t>
+          <t>11918; 25424</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17707; 33627</t>
+          <t>17071; 33683</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8073; 19699</t>
+          <t>8150; 20111</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>10908; 25233</t>
+          <t>10463; 25992</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP28_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP28_R-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,5%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,34%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,71%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1,33; 10,95</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0,94; 8,3</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 9,45</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,65; 8,17</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0,0; 8,93</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,52</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,12</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,18; 10,73</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,94; 8,39</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,42</t>
+          <t>0,0; 7,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,65</t>
+          <t>0,0; 7,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,37</t>
+          <t>0,62; 6,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,33</t>
+          <t>1,05; 6,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,7</t>
+          <t>0,61; 5,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,5</t>
+          <t>0,84; 5,32</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>2,29%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,61%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,32</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,97</t>
+          <t>0,0; 4,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,02</t>
+          <t>0,0; 4,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,65; 6,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,14</t>
+          <t>0,0; 5,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,58</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,88</t>
+          <t>0,0; 3,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,3</t>
+          <t>0,32; 3,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,74</t>
+          <t>0,46; 3,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,03</t>
+          <t>0,29; 2,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
     </row>
@@ -929,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,49%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 6,3</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,17</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,82</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,73</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,65</t>
+          <t>0,0; 8,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 5,74</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 3,38</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0,53; 5,14</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,24</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0,53; 4,69</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,69%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,02%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -1137,42 +1137,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,99</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,61</t>
+          <t>0,0; 6,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,88</t>
+          <t>0,0; 4,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 12,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,85</t>
+          <t>0,0; 5,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,25</t>
+          <t>0,0; 7,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,59</t>
+          <t>0,0; 5,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,48; 13,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,5</t>
+          <t>0,44; 4,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,05</t>
+          <t>0,0; 3,26</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,24</t>
+          <t>0,76; 6,43</t>
         </is>
       </c>
     </row>
@@ -1209,44 +1209,44 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>1,53%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,98%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
           <t>1,51%</t>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,82</t>
+          <t>0,0; 7,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,11</t>
+          <t>0,0; 10,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 12,53</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 7,78</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 8,19</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 7,17</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,83</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,27</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 10,48</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,3</t>
+          <t>0,0; 4,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,17</t>
+          <t>0,8; 8,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,43</t>
+          <t>0,0; 4,04</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,6</t>
+          <t>0,0; 4,92</t>
         </is>
       </c>
     </row>
@@ -1349,44 +1349,44 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4,07%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1,19%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
           <t>0,56%</t>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -1417,52 +1417,52 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 12,02</t>
+          <t>0,0; 8,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>0,0; 6,1</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,19</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1,29; 11,56</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,87</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,15</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,05</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,05</t>
+          <t>0,0; 3,06</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,29; 6,83</t>
+          <t>1,29; 7,3</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,9</t>
+          <t>0,0; 3,5</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>0,54%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>2,06%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1557,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,89</t>
+          <t>0,0; 3,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,46</t>
+          <t>0,51; 4,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 7,0</t>
+          <t>0,0; 4,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,78</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,98</t>
+          <t>0,0; 2,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,35</t>
+          <t>0,55; 4,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,79</t>
+          <t>0,84; 7,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,23</t>
+          <t>0,28; 2,52</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1607,12 +1607,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,84</t>
+          <t>0,78; 3,68</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,72</t>
+          <t>0,8; 4,68</t>
         </is>
       </c>
     </row>
@@ -1629,44 +1629,44 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>2,11%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>2,39%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
           <t>1,46%</t>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,76</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,85</t>
+          <t>0,38; 3,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,43</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,78; 4,53</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,9; 5,18</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,86</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,95</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,39; 3,85</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,6</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,91</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,1</t>
+          <t>0,64; 3,1</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,42</t>
+          <t>0,9; 3,58</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,92</t>
+          <t>0,18; 1,63</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
     </row>
@@ -1769,62 +1769,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2,02%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>1,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,17</t>
+          <t>0,65; 1,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,02</t>
+          <t>0,97; 2,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,77</t>
+          <t>0,58; 1,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,55</t>
+          <t>0,52; 1,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,07</t>
+          <t>0,69; 2,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,62</t>
+          <t>1,16; 3,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,75</t>
+          <t>0,49; 1,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,78</t>
+          <t>0,84; 2,84</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,83</t>
+          <t>0,83; 1,81</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,52</t>
+          <t>1,34; 2,59</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,55</t>
+          <t>0,62; 1,55</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,83</t>
+          <t>0,82; 2,01</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,49 +2141,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2835</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1832</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1261</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1681</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1312</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>638</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1295</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1170</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2835</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1832</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1261</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1793</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2835</t>
-        </is>
-      </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t>3145</t>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>2851</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>800; 6593</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>566; 4990</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4970</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>420; 5238</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4684</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3096</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4484</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>708; 6458</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>567; 5044</t>
+          <t>0; 4680</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4432</t>
+          <t>0; 3678</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>488; 5280</t>
+          <t>0; 4291</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>708; 7025</t>
+          <t>687; 7694</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1210; 7121</t>
+          <t>1179; 6965</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>621; 5701</t>
+          <t>612; 5159</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1087; 6870</t>
+          <t>1012; 6416</t>
         </is>
       </c>
     </row>
@@ -2281,37 +2281,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2309</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1579</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>571</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1315</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1353</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>751</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1739</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>657; 6375</t>
+          <t>0; 3444</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5775</t>
+          <t>0; 4804</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2337</t>
+          <t>0; 4793</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5023</t>
+          <t>0; 5231</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2619</t>
+          <t>657; 6445</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4109</t>
+          <t>0; 5752</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4676</t>
+          <t>0; 2747</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4953</t>
+          <t>0; 3385</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>661; 6897</t>
+          <t>659; 7228</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>678; 7332</t>
+          <t>910; 7217</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>570; 5934</t>
+          <t>566; 5096</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 6221</t>
+          <t>0; 5068</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,62 +2557,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1265</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1495</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>1265</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2146</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2146</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>642</t>
         </is>
       </c>
     </row>
@@ -2625,32 +2625,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0; 4430</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3252</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4691</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3338</t>
-        </is>
-      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4421</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3550</t>
+          <t>0; 5246</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2660,27 +2660,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>0; 3248</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4646</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>648; 6315</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4453</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>648; 5756</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3637</t>
+          <t>0; 3267</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1252</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1448</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>753</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3730</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3730</t>
+          <t>3947</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4444</t>
+          <t>0; 3028</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5464</t>
+          <t>0; 4709</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4226</t>
+          <t>0; 3197</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>960; 8637</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 2975</t>
+          <t>0; 3843</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4615</t>
+          <t>0; 5205</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3230</t>
+          <t>0; 3840</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1050; 9261</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>594; 4880</t>
+          <t>590; 4880</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>654; 6556</t>
+          <t>646; 6578</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 4338</t>
+          <t>0; 4641</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>950; 9252</t>
+          <t>1083; 9195</t>
         </is>
       </c>
     </row>
@@ -2910,37 +2910,37 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,44 +2973,44 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>746</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>688</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1299</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>860</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
           <t>1307</t>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>841</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3275</t>
+          <t>0; 3336</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3808</t>
+          <t>0; 4647</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2856</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>0; 4958</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3255</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3082</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3021</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0; 3509</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0; 3989</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0; 4266</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4596</t>
+          <t>0; 4262</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>640; 4981</t>
+          <t>643; 6682</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 3842</t>
+          <t>0; 3510</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 4213</t>
+          <t>0; 3698</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,44 +3181,44 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1452</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>640</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2204</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>608</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1452</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>801</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
           <t>640</t>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>637</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2606</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>712; 6516</t>
+          <t>0; 4511</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3406</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
+          <t>0; 2986</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2871</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>698; 6264</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3008</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0; 5141</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0; 3964</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3488</t>
+          <t>0; 3499</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1426; 7539</t>
+          <t>1420; 8063</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 3709</t>
+          <t>0; 3705</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 3996</t>
+          <t>0; 3317</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1270</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2107</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1774</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>733</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>665</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>2591</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>3149</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1445</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>1270</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2107</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>5498</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3656</t>
+          <t>0; 4701</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 3434</t>
+          <t>0; 3882</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>625; 5599</t>
+          <t>662; 5656</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>878; 8718</t>
+          <t>0; 5811</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 5058</t>
+          <t>0; 4186</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3864</t>
+          <t>0; 2703</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 5650</t>
+          <t>685; 6090</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 5883</t>
+          <t>1026; 9205</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>718; 5808</t>
+          <t>720; 6556</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>620; 5213</t>
+          <t>620; 5218</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2079; 9804</t>
+          <t>1984; 9394</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1630; 10406</t>
+          <t>2113; 12313</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,44 +3597,44 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2599</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1297</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>3256</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>3601</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>1359</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>2599</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1297</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
           <t>4615</t>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1111</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1229; 7354</t>
+          <t>0; 4739</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1321; 7323</t>
+          <t>629; 5975</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 2656</t>
+          <t>0; 4505</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
+          <t>0; 3804</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1199; 7003</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>1360; 7813</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2591</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>0; 4778</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>635; 6317</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>0; 3953</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>0; 4483</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2104; 9807</t>
+          <t>2013; 9824</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2949; 10786</t>
+          <t>2852; 11280</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>525; 5588</t>
+          <t>521; 4760</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 4571</t>
+          <t>0; 4321</t>
         </is>
       </c>
     </row>
@@ -3742,37 +3742,37 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>8810</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>11419</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>6661</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>8832</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>13052</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>6372</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>9542</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>8810</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>11419</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>6661</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>16995</t>
+          <t>17268</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>4925; 14519</t>
+          <t>4679; 14251</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>8273; 19521</t>
+          <t>6709; 18126</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3221; 11189</t>
+          <t>3878; 11530</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5014; 16868</t>
+          <t>3633; 12623</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4886; 14795</t>
+          <t>4603; 14566</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6996; 18066</t>
+          <t>7493; 19592</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3262; 11672</t>
+          <t>3113; 11453</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>3723; 13517</t>
+          <t>5245; 17750</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>11918; 25424</t>
+          <t>11480; 25050</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17071; 33683</t>
+          <t>17910; 34532</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8150; 20111</t>
+          <t>8009; 20213</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>10463; 25992</t>
+          <t>10858; 26537</t>
         </is>
       </c>
     </row>
